--- a/outputs/forecasts/xgb_forecast_segments.xlsx
+++ b/outputs/forecasts/xgb_forecast_segments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D193"/>
+  <dimension ref="A1:D205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,7 +469,7 @@
         <v>46053</v>
       </c>
       <c r="D2" t="n">
-        <v>67028.6640625</v>
+        <v>71123.34371303659</v>
       </c>
     </row>
     <row r="3">
@@ -487,7 +487,7 @@
         <v>46081</v>
       </c>
       <c r="D3" t="n">
-        <v>53839.0078125</v>
+        <v>70218.20289243879</v>
       </c>
     </row>
     <row r="4">
@@ -505,7 +505,7 @@
         <v>46112</v>
       </c>
       <c r="D4" t="n">
-        <v>61862.15234375</v>
+        <v>69608.19375380396</v>
       </c>
     </row>
     <row r="5">
@@ -523,7 +523,7 @@
         <v>46142</v>
       </c>
       <c r="D5" t="n">
-        <v>68676.9375</v>
+        <v>69697.87054443487</v>
       </c>
     </row>
     <row r="6">
@@ -541,7 +541,7 @@
         <v>46173</v>
       </c>
       <c r="D6" t="n">
-        <v>64872.30078125</v>
+        <v>69959.85475677619</v>
       </c>
     </row>
     <row r="7">
@@ -559,7 +559,7 @@
         <v>46203</v>
       </c>
       <c r="D7" t="n">
-        <v>64416.90234375</v>
+        <v>71616.33318399334</v>
       </c>
     </row>
     <row r="8">
@@ -577,7 +577,7 @@
         <v>46234</v>
       </c>
       <c r="D8" t="n">
-        <v>66402.78125</v>
+        <v>69696.74056320853</v>
       </c>
     </row>
     <row r="9">
@@ -595,7 +595,7 @@
         <v>46265</v>
       </c>
       <c r="D9" t="n">
-        <v>65728.796875</v>
+        <v>69435.74164135569</v>
       </c>
     </row>
     <row r="10">
@@ -613,7 +613,7 @@
         <v>46295</v>
       </c>
       <c r="D10" t="n">
-        <v>66265.921875</v>
+        <v>65912.33412662306</v>
       </c>
     </row>
     <row r="11">
@@ -631,7 +631,7 @@
         <v>46326</v>
       </c>
       <c r="D11" t="n">
-        <v>71682.1171875</v>
+        <v>66916.29483421952</v>
       </c>
     </row>
     <row r="12">
@@ -649,7 +649,7 @@
         <v>46356</v>
       </c>
       <c r="D12" t="n">
-        <v>70022.734375</v>
+        <v>66916.29483421952</v>
       </c>
     </row>
     <row r="13">
@@ -667,7 +667,7 @@
         <v>46387</v>
       </c>
       <c r="D13" t="n">
-        <v>69571.265625</v>
+        <v>66981.0368804699</v>
       </c>
     </row>
     <row r="14">
@@ -685,7 +685,7 @@
         <v>46053</v>
       </c>
       <c r="D14" t="n">
-        <v>31946.923828125</v>
+        <v>30681.43726963345</v>
       </c>
     </row>
     <row r="15">
@@ -703,7 +703,7 @@
         <v>46081</v>
       </c>
       <c r="D15" t="n">
-        <v>31368.927734375</v>
+        <v>30686.38278601326</v>
       </c>
     </row>
     <row r="16">
@@ -721,7 +721,7 @@
         <v>46112</v>
       </c>
       <c r="D16" t="n">
-        <v>27822.498046875</v>
+        <v>29229.2375318287</v>
       </c>
     </row>
     <row r="17">
@@ -739,7 +739,7 @@
         <v>46142</v>
       </c>
       <c r="D17" t="n">
-        <v>28873.658203125</v>
+        <v>28687.6665787416</v>
       </c>
     </row>
     <row r="18">
@@ -757,7 +757,7 @@
         <v>46173</v>
       </c>
       <c r="D18" t="n">
-        <v>27545.259765625</v>
+        <v>28162.44082371948</v>
       </c>
     </row>
     <row r="19">
@@ -775,7 +775,7 @@
         <v>46203</v>
       </c>
       <c r="D19" t="n">
-        <v>31555.298828125</v>
+        <v>28790.75096108587</v>
       </c>
     </row>
     <row r="20">
@@ -793,7 +793,7 @@
         <v>46234</v>
       </c>
       <c r="D20" t="n">
-        <v>30493.65625</v>
+        <v>27356.01351018785</v>
       </c>
     </row>
     <row r="21">
@@ -811,7 +811,7 @@
         <v>46265</v>
       </c>
       <c r="D21" t="n">
-        <v>28509.859375</v>
+        <v>27080.80435502819</v>
       </c>
     </row>
     <row r="22">
@@ -829,7 +829,7 @@
         <v>46295</v>
       </c>
       <c r="D22" t="n">
-        <v>30227.427734375</v>
+        <v>27021.26068261326</v>
       </c>
     </row>
     <row r="23">
@@ -847,7 +847,7 @@
         <v>46326</v>
       </c>
       <c r="D23" t="n">
-        <v>32168.169921875</v>
+        <v>28695.10936732812</v>
       </c>
     </row>
     <row r="24">
@@ -865,7 +865,7 @@
         <v>46356</v>
       </c>
       <c r="D24" t="n">
-        <v>30787.185546875</v>
+        <v>28845.60923182948</v>
       </c>
     </row>
     <row r="25">
@@ -883,7 +883,7 @@
         <v>46387</v>
       </c>
       <c r="D25" t="n">
-        <v>30038.658203125</v>
+        <v>29043.4506907279</v>
       </c>
     </row>
     <row r="26">
@@ -901,7 +901,7 @@
         <v>46053</v>
       </c>
       <c r="D26" t="n">
-        <v>3627.821533203125</v>
+        <v>2035.558489629854</v>
       </c>
     </row>
     <row r="27">
@@ -919,7 +919,7 @@
         <v>46081</v>
       </c>
       <c r="D27" t="n">
-        <v>2744.435302734375</v>
+        <v>1969.437607641926</v>
       </c>
     </row>
     <row r="28">
@@ -937,7 +937,7 @@
         <v>46112</v>
       </c>
       <c r="D28" t="n">
-        <v>2688.552001953125</v>
+        <v>1496.725238364422</v>
       </c>
     </row>
     <row r="29">
@@ -955,7 +955,7 @@
         <v>46142</v>
       </c>
       <c r="D29" t="n">
-        <v>2549.171142578125</v>
+        <v>1535.671834539265</v>
       </c>
     </row>
     <row r="30">
@@ -973,7 +973,7 @@
         <v>46173</v>
       </c>
       <c r="D30" t="n">
-        <v>2590.014404296875</v>
+        <v>1548.898744172651</v>
       </c>
     </row>
     <row r="31">
@@ -991,7 +991,7 @@
         <v>46203</v>
       </c>
       <c r="D31" t="n">
-        <v>1953.013793945312</v>
+        <v>1499.640461359846</v>
       </c>
     </row>
     <row r="32">
@@ -1009,7 +1009,7 @@
         <v>46234</v>
       </c>
       <c r="D32" t="n">
-        <v>2112.415283203125</v>
+        <v>1501.45407275524</v>
       </c>
     </row>
     <row r="33">
@@ -1027,7 +1027,7 @@
         <v>46265</v>
       </c>
       <c r="D33" t="n">
-        <v>2162.19580078125</v>
+        <v>1553.954679588948</v>
       </c>
     </row>
     <row r="34">
@@ -1045,7 +1045,7 @@
         <v>46295</v>
       </c>
       <c r="D34" t="n">
-        <v>2404.751953125</v>
+        <v>1572.181969372695</v>
       </c>
     </row>
     <row r="35">
@@ -1063,7 +1063,7 @@
         <v>46326</v>
       </c>
       <c r="D35" t="n">
-        <v>2934.837890625</v>
+        <v>1721.825086543851</v>
       </c>
     </row>
     <row r="36">
@@ -1081,7 +1081,7 @@
         <v>46356</v>
       </c>
       <c r="D36" t="n">
-        <v>2303.55908203125</v>
+        <v>1667.9540512538</v>
       </c>
     </row>
     <row r="37">
@@ -1099,7 +1099,7 @@
         <v>46387</v>
       </c>
       <c r="D37" t="n">
-        <v>2136.56640625</v>
+        <v>1677.708952526465</v>
       </c>
     </row>
     <row r="38">
@@ -1117,7 +1117,7 @@
         <v>46053</v>
       </c>
       <c r="D38" t="n">
-        <v>14974.71875</v>
+        <v>16923.69962623279</v>
       </c>
     </row>
     <row r="39">
@@ -1135,7 +1135,7 @@
         <v>46081</v>
       </c>
       <c r="D39" t="n">
-        <v>13905.328125</v>
+        <v>17250.49930685591</v>
       </c>
     </row>
     <row r="40">
@@ -1153,7 +1153,7 @@
         <v>46112</v>
       </c>
       <c r="D40" t="n">
-        <v>13936.2138671875</v>
+        <v>16948.97860533943</v>
       </c>
     </row>
     <row r="41">
@@ -1171,7 +1171,7 @@
         <v>46142</v>
       </c>
       <c r="D41" t="n">
-        <v>14155.8828125</v>
+        <v>16970.81508412362</v>
       </c>
     </row>
     <row r="42">
@@ -1189,7 +1189,7 @@
         <v>46173</v>
       </c>
       <c r="D42" t="n">
-        <v>14308.9365234375</v>
+        <v>16970.81508412362</v>
       </c>
     </row>
     <row r="43">
@@ -1207,7 +1207,7 @@
         <v>46203</v>
       </c>
       <c r="D43" t="n">
-        <v>14193.12890625</v>
+        <v>17260.80152895594</v>
       </c>
     </row>
     <row r="44">
@@ -1225,7 +1225,7 @@
         <v>46234</v>
       </c>
       <c r="D44" t="n">
-        <v>14271.7373046875</v>
+        <v>16954.41083474121</v>
       </c>
     </row>
     <row r="45">
@@ -1243,7 +1243,7 @@
         <v>46265</v>
       </c>
       <c r="D45" t="n">
-        <v>14379.6552734375</v>
+        <v>16954.41083474121</v>
       </c>
     </row>
     <row r="46">
@@ -1261,7 +1261,7 @@
         <v>46295</v>
       </c>
       <c r="D46" t="n">
-        <v>14991.76953125</v>
+        <v>16839.33358798347</v>
       </c>
     </row>
     <row r="47">
@@ -1279,7 +1279,7 @@
         <v>46326</v>
       </c>
       <c r="D47" t="n">
-        <v>15641.4677734375</v>
+        <v>18146.07876802858</v>
       </c>
     </row>
     <row r="48">
@@ -1297,7 +1297,7 @@
         <v>46356</v>
       </c>
       <c r="D48" t="n">
-        <v>15060.3154296875</v>
+        <v>18146.07876802858</v>
       </c>
     </row>
     <row r="49">
@@ -1315,7 +1315,7 @@
         <v>46387</v>
       </c>
       <c r="D49" t="n">
-        <v>14812.677734375</v>
+        <v>18163.63594836319</v>
       </c>
     </row>
     <row r="50">
@@ -1333,7 +1333,7 @@
         <v>46053</v>
       </c>
       <c r="D50" t="n">
-        <v>3771.904296875</v>
+        <v>2133.623718229718</v>
       </c>
     </row>
     <row r="51">
@@ -1351,7 +1351,7 @@
         <v>46081</v>
       </c>
       <c r="D51" t="n">
-        <v>2921.9921875</v>
+        <v>2429.125463067048</v>
       </c>
     </row>
     <row r="52">
@@ -1369,7 +1369,7 @@
         <v>46112</v>
       </c>
       <c r="D52" t="n">
-        <v>3018.9638671875</v>
+        <v>2167.210201564028</v>
       </c>
     </row>
     <row r="53">
@@ -1387,7 +1387,7 @@
         <v>46142</v>
       </c>
       <c r="D53" t="n">
-        <v>2989.382080078125</v>
+        <v>2368.152354279968</v>
       </c>
     </row>
     <row r="54">
@@ -1405,7 +1405,7 @@
         <v>46173</v>
       </c>
       <c r="D54" t="n">
-        <v>2989.382080078125</v>
+        <v>2237.289240470061</v>
       </c>
     </row>
     <row r="55">
@@ -1423,7 +1423,7 @@
         <v>46203</v>
       </c>
       <c r="D55" t="n">
-        <v>2594.340576171875</v>
+        <v>2261.40039901237</v>
       </c>
     </row>
     <row r="56">
@@ -1441,7 +1441,7 @@
         <v>46234</v>
       </c>
       <c r="D56" t="n">
-        <v>2600.648681640625</v>
+        <v>2236.50918050955</v>
       </c>
     </row>
     <row r="57">
@@ -1459,7 +1459,7 @@
         <v>46265</v>
       </c>
       <c r="D57" t="n">
-        <v>2650.42919921875</v>
+        <v>2236.50918050955</v>
       </c>
     </row>
     <row r="58">
@@ -1477,7 +1477,7 @@
         <v>46295</v>
       </c>
       <c r="D58" t="n">
-        <v>2892.9853515625</v>
+        <v>2221.320971069405</v>
       </c>
     </row>
     <row r="59">
@@ -1495,7 +1495,7 @@
         <v>46326</v>
       </c>
       <c r="D59" t="n">
-        <v>3543.7392578125</v>
+        <v>2433.058044654099</v>
       </c>
     </row>
     <row r="60">
@@ -1513,7 +1513,7 @@
         <v>46356</v>
       </c>
       <c r="D60" t="n">
-        <v>2871.1123046875</v>
+        <v>2433.058044654099</v>
       </c>
     </row>
     <row r="61">
@@ -1531,7 +1531,7 @@
         <v>46387</v>
       </c>
       <c r="D61" t="n">
-        <v>2774.22216796875</v>
+        <v>2435.412979934934</v>
       </c>
     </row>
     <row r="62">
@@ -1549,7 +1549,7 @@
         <v>46053</v>
       </c>
       <c r="D62" t="n">
-        <v>82631.4765625</v>
+        <v>77731.61448624513</v>
       </c>
     </row>
     <row r="63">
@@ -1567,7 +1567,7 @@
         <v>46081</v>
       </c>
       <c r="D63" t="n">
-        <v>83499.984375</v>
+        <v>73028.85851272114</v>
       </c>
     </row>
     <row r="64">
@@ -1585,7 +1585,7 @@
         <v>46112</v>
       </c>
       <c r="D64" t="n">
-        <v>80517.9453125</v>
+        <v>75478.5451886646</v>
       </c>
     </row>
     <row r="65">
@@ -1603,7 +1603,7 @@
         <v>46142</v>
       </c>
       <c r="D65" t="n">
-        <v>85206.0546875</v>
+        <v>76759.7232181322</v>
       </c>
     </row>
     <row r="66">
@@ -1621,7 +1621,7 @@
         <v>46173</v>
       </c>
       <c r="D66" t="n">
-        <v>86715.6484375</v>
+        <v>76576.63726528356</v>
       </c>
     </row>
     <row r="67">
@@ -1639,7 +1639,7 @@
         <v>46203</v>
       </c>
       <c r="D67" t="n">
-        <v>119714.6015625</v>
+        <v>79009.43149172587</v>
       </c>
     </row>
     <row r="68">
@@ -1657,7 +1657,7 @@
         <v>46234</v>
       </c>
       <c r="D68" t="n">
-        <v>84447.9296875</v>
+        <v>76725.03201752165</v>
       </c>
     </row>
     <row r="69">
@@ -1675,7 +1675,7 @@
         <v>46265</v>
       </c>
       <c r="D69" t="n">
-        <v>84366.390625</v>
+        <v>76732.78860405998</v>
       </c>
     </row>
     <row r="70">
@@ -1693,7 +1693,7 @@
         <v>46295</v>
       </c>
       <c r="D70" t="n">
-        <v>83653.9375</v>
+        <v>76564.07711379518</v>
       </c>
     </row>
     <row r="71">
@@ -1711,7 +1711,7 @@
         <v>46326</v>
       </c>
       <c r="D71" t="n">
-        <v>89163.2421875</v>
+        <v>79067.24625213596</v>
       </c>
     </row>
     <row r="72">
@@ -1729,7 +1729,7 @@
         <v>46356</v>
       </c>
       <c r="D72" t="n">
-        <v>86115.765625</v>
+        <v>78462.332745451</v>
       </c>
     </row>
     <row r="73">
@@ -1747,7 +1747,7 @@
         <v>46387</v>
       </c>
       <c r="D73" t="n">
-        <v>87406.4921875</v>
+        <v>79143.74426462247</v>
       </c>
     </row>
     <row r="74">
@@ -1765,7 +1765,7 @@
         <v>46053</v>
       </c>
       <c r="D74" t="n">
-        <v>8292.87109375</v>
+        <v>6959.703406526471</v>
       </c>
     </row>
     <row r="75">
@@ -1783,7 +1783,7 @@
         <v>46081</v>
       </c>
       <c r="D75" t="n">
-        <v>8423.7060546875</v>
+        <v>7960.504253937132</v>
       </c>
     </row>
     <row r="76">
@@ -1801,7 +1801,7 @@
         <v>46112</v>
       </c>
       <c r="D76" t="n">
-        <v>6974.08447265625</v>
+        <v>7657.154202796455</v>
       </c>
     </row>
     <row r="77">
@@ -1819,7 +1819,7 @@
         <v>46142</v>
       </c>
       <c r="D77" t="n">
-        <v>8635.6044921875</v>
+        <v>7721.642878976278</v>
       </c>
     </row>
     <row r="78">
@@ -1837,7 +1837,7 @@
         <v>46173</v>
       </c>
       <c r="D78" t="n">
-        <v>7933.92626953125</v>
+        <v>7721.642878976278</v>
       </c>
     </row>
     <row r="79">
@@ -1855,7 +1855,7 @@
         <v>46203</v>
       </c>
       <c r="D79" t="n">
-        <v>7368.44091796875</v>
+        <v>7781.848616430084</v>
       </c>
     </row>
     <row r="80">
@@ -1873,7 +1873,7 @@
         <v>46234</v>
       </c>
       <c r="D80" t="n">
-        <v>7841.041015625</v>
+        <v>7705.207237628978</v>
       </c>
     </row>
     <row r="81">
@@ -1891,7 +1891,7 @@
         <v>46265</v>
       </c>
       <c r="D81" t="n">
-        <v>7916.13525390625</v>
+        <v>7705.207237628978</v>
       </c>
     </row>
     <row r="82">
@@ -1909,7 +1909,7 @@
         <v>46295</v>
       </c>
       <c r="D82" t="n">
-        <v>8390.4501953125</v>
+        <v>7652.904812138119</v>
       </c>
     </row>
     <row r="83">
@@ -1927,7 +1927,7 @@
         <v>46326</v>
       </c>
       <c r="D83" t="n">
-        <v>8973.9892578125</v>
+        <v>8231.847799076839</v>
       </c>
     </row>
     <row r="84">
@@ -1945,7 +1945,7 @@
         <v>46356</v>
       </c>
       <c r="D84" t="n">
-        <v>8553.5703125</v>
+        <v>8231.847799076839</v>
       </c>
     </row>
     <row r="85">
@@ -1963,7 +1963,7 @@
         <v>46387</v>
       </c>
       <c r="D85" t="n">
-        <v>8591.4404296875</v>
+        <v>8211.835247569499</v>
       </c>
     </row>
     <row r="86">
@@ -1981,7 +1981,7 @@
         <v>46053</v>
       </c>
       <c r="D86" t="n">
-        <v>21212.50390625</v>
+        <v>17977.31754656728</v>
       </c>
     </row>
     <row r="87">
@@ -1999,7 +1999,7 @@
         <v>46081</v>
       </c>
       <c r="D87" t="n">
-        <v>19592.7734375</v>
+        <v>18284.91997573266</v>
       </c>
     </row>
     <row r="88">
@@ -2017,7 +2017,7 @@
         <v>46112</v>
       </c>
       <c r="D88" t="n">
-        <v>17321.369140625</v>
+        <v>17740.48370806179</v>
       </c>
     </row>
     <row r="89">
@@ -2035,7 +2035,7 @@
         <v>46142</v>
       </c>
       <c r="D89" t="n">
-        <v>21278.79296875</v>
+        <v>17682.81413523169</v>
       </c>
     </row>
     <row r="90">
@@ -2053,7 +2053,7 @@
         <v>46173</v>
       </c>
       <c r="D90" t="n">
-        <v>20687.130859375</v>
+        <v>17682.81413523169</v>
       </c>
     </row>
     <row r="91">
@@ -2071,7 +2071,7 @@
         <v>46203</v>
       </c>
       <c r="D91" t="n">
-        <v>23051.404296875</v>
+        <v>18127.1381481243</v>
       </c>
     </row>
     <row r="92">
@@ -2089,7 +2089,7 @@
         <v>46234</v>
       </c>
       <c r="D92" t="n">
-        <v>26530.1796875</v>
+        <v>17665.7216972297</v>
       </c>
     </row>
     <row r="93">
@@ -2107,7 +2107,7 @@
         <v>46265</v>
       </c>
       <c r="D93" t="n">
-        <v>27632.91796875</v>
+        <v>17665.7216972297</v>
       </c>
     </row>
     <row r="94">
@@ -2125,7 +2125,7 @@
         <v>46295</v>
       </c>
       <c r="D94" t="n">
-        <v>29988.71875</v>
+        <v>17626.87858782698</v>
       </c>
     </row>
     <row r="95">
@@ -2143,7 +2143,7 @@
         <v>46326</v>
       </c>
       <c r="D95" t="n">
-        <v>32630.849609375</v>
+        <v>18907.38230563938</v>
       </c>
     </row>
     <row r="96">
@@ -2161,7 +2161,7 @@
         <v>46356</v>
       </c>
       <c r="D96" t="n">
-        <v>31126.580078125</v>
+        <v>18907.38230563938</v>
       </c>
     </row>
     <row r="97">
@@ -2179,7 +2179,7 @@
         <v>46387</v>
       </c>
       <c r="D97" t="n">
-        <v>31358.759765625</v>
+        <v>18925.67604218065</v>
       </c>
     </row>
     <row r="98">
@@ -2197,7 +2197,7 @@
         <v>46053</v>
       </c>
       <c r="D98" t="n">
-        <v>32284.943359375</v>
+        <v>29778.81670124081</v>
       </c>
     </row>
     <row r="99">
@@ -2215,7 +2215,7 @@
         <v>46081</v>
       </c>
       <c r="D99" t="n">
-        <v>27678.546875</v>
+        <v>29735.82139568763</v>
       </c>
     </row>
     <row r="100">
@@ -2233,7 +2233,7 @@
         <v>46112</v>
       </c>
       <c r="D100" t="n">
-        <v>26745.376953125</v>
+        <v>27735.93641224065</v>
       </c>
     </row>
     <row r="101">
@@ -2251,7 +2251,7 @@
         <v>46142</v>
       </c>
       <c r="D101" t="n">
-        <v>27040.447265625</v>
+        <v>27746.70446746723</v>
       </c>
     </row>
     <row r="102">
@@ -2269,7 +2269,7 @@
         <v>46173</v>
       </c>
       <c r="D102" t="n">
-        <v>26961.54296875</v>
+        <v>27238.78357194995</v>
       </c>
     </row>
     <row r="103">
@@ -2287,7 +2287,7 @@
         <v>46203</v>
       </c>
       <c r="D103" t="n">
-        <v>26684.421875</v>
+        <v>27678.56852034178</v>
       </c>
     </row>
     <row r="104">
@@ -2305,7 +2305,7 @@
         <v>46234</v>
       </c>
       <c r="D104" t="n">
-        <v>26438.046875</v>
+        <v>27110.80636519167</v>
       </c>
     </row>
     <row r="105">
@@ -2323,7 +2323,7 @@
         <v>46265</v>
       </c>
       <c r="D105" t="n">
-        <v>26570.1328125</v>
+        <v>27110.80636519167</v>
       </c>
     </row>
     <row r="106">
@@ -2341,7 +2341,7 @@
         <v>46295</v>
       </c>
       <c r="D106" t="n">
-        <v>28615.8671875</v>
+        <v>27051.19672856544</v>
       </c>
     </row>
     <row r="107">
@@ -2359,7 +2359,7 @@
         <v>46326</v>
       </c>
       <c r="D107" t="n">
-        <v>32458.255859375</v>
+        <v>28884.75537378177</v>
       </c>
     </row>
     <row r="108">
@@ -2377,7 +2377,7 @@
         <v>46356</v>
       </c>
       <c r="D108" t="n">
-        <v>30307.544921875</v>
+        <v>28759.76761453079</v>
       </c>
     </row>
     <row r="109">
@@ -2395,7 +2395,7 @@
         <v>46387</v>
       </c>
       <c r="D109" t="n">
-        <v>30642.57421875</v>
+        <v>28992.36341752461</v>
       </c>
     </row>
     <row r="110">
@@ -2413,7 +2413,7 @@
         <v>46053</v>
       </c>
       <c r="D110" t="n">
-        <v>53055.76171875</v>
+        <v>52364.38859912965</v>
       </c>
     </row>
     <row r="111">
@@ -2431,7 +2431,7 @@
         <v>46081</v>
       </c>
       <c r="D111" t="n">
-        <v>47503.0078125</v>
+        <v>47135.46899231514</v>
       </c>
     </row>
     <row r="112">
@@ -2449,7 +2449,7 @@
         <v>46112</v>
       </c>
       <c r="D112" t="n">
-        <v>45910.91015625</v>
+        <v>44076.28444286506</v>
       </c>
     </row>
     <row r="113">
@@ -2467,7 +2467,7 @@
         <v>46142</v>
       </c>
       <c r="D113" t="n">
-        <v>49800.18359375</v>
+        <v>47923.35148500653</v>
       </c>
     </row>
     <row r="114">
@@ -2485,7 +2485,7 @@
         <v>46173</v>
       </c>
       <c r="D114" t="n">
-        <v>50904.1015625</v>
+        <v>46617.86785435864</v>
       </c>
     </row>
     <row r="115">
@@ -2503,7 +2503,7 @@
         <v>46203</v>
       </c>
       <c r="D115" t="n">
-        <v>51253.44921875</v>
+        <v>45436.51830763344</v>
       </c>
     </row>
     <row r="116">
@@ -2521,7 +2521,7 @@
         <v>46234</v>
       </c>
       <c r="D116" t="n">
-        <v>51670.77734375</v>
+        <v>45140.95882401228</v>
       </c>
     </row>
     <row r="117">
@@ -2539,7 +2539,7 @@
         <v>46265</v>
       </c>
       <c r="D117" t="n">
-        <v>51649.94140625</v>
+        <v>45140.95882401228</v>
       </c>
     </row>
     <row r="118">
@@ -2557,7 +2557,7 @@
         <v>46295</v>
       </c>
       <c r="D118" t="n">
-        <v>51549.7109375</v>
+        <v>44188.45119274654</v>
       </c>
     </row>
     <row r="119">
@@ -2575,7 +2575,7 @@
         <v>46326</v>
       </c>
       <c r="D119" t="n">
-        <v>54008.75390625</v>
+        <v>47329.11794498626</v>
       </c>
     </row>
     <row r="120">
@@ -2593,7 +2593,7 @@
         <v>46356</v>
       </c>
       <c r="D120" t="n">
-        <v>54850.6640625</v>
+        <v>47329.11794498626</v>
       </c>
     </row>
     <row r="121">
@@ -2611,7 +2611,7 @@
         <v>46387</v>
       </c>
       <c r="D121" t="n">
-        <v>56660.62890625</v>
+        <v>46366.42019857802</v>
       </c>
     </row>
     <row r="122">
@@ -2622,14 +2622,14 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Location de salles</t>
+          <t>Certificat de commercialisation libre</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
-        <v>46053</v>
+        <v>46022</v>
       </c>
       <c r="D122" t="n">
-        <v>3411.61083984375</v>
+        <v>500.6014411530666</v>
       </c>
     </row>
     <row r="123">
@@ -2640,14 +2640,14 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Location de salles</t>
+          <t>Certificat de commercialisation libre</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="D123" t="n">
-        <v>2555.52001953125</v>
+        <v>513.1017228270764</v>
       </c>
     </row>
     <row r="124">
@@ -2658,14 +2658,14 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Location de salles</t>
+          <t>Certificat de commercialisation libre</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>46112</v>
+        <v>46081</v>
       </c>
       <c r="D124" t="n">
-        <v>2499.63671875</v>
+        <v>451.9202133633913</v>
       </c>
     </row>
     <row r="125">
@@ -2676,14 +2676,14 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Location de salles</t>
+          <t>Certificat de commercialisation libre</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
-        <v>46142</v>
+        <v>46112</v>
       </c>
       <c r="D125" t="n">
-        <v>2484.66845703125</v>
+        <v>412.1853234382691</v>
       </c>
     </row>
     <row r="126">
@@ -2694,14 +2694,14 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Location de salles</t>
+          <t>Certificat de commercialisation libre</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>46173</v>
+        <v>46142</v>
       </c>
       <c r="D126" t="n">
-        <v>2484.66845703125</v>
+        <v>413.5246786402317</v>
       </c>
     </row>
     <row r="127">
@@ -2712,14 +2712,14 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Location de salles</t>
+          <t>Certificat de commercialisation libre</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="D127" t="n">
-        <v>2059.922119140625</v>
+        <v>413.5246786402317</v>
       </c>
     </row>
     <row r="128">
@@ -2730,14 +2730,14 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Location de salles</t>
+          <t>Certificat de commercialisation libre</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="D128" t="n">
-        <v>2219.324462890625</v>
+        <v>400.3504155278067</v>
       </c>
     </row>
     <row r="129">
@@ -2748,14 +2748,14 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Location de salles</t>
+          <t>Certificat de commercialisation libre</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="D129" t="n">
-        <v>2132.60009765625</v>
+        <v>400.8354708797646</v>
       </c>
     </row>
     <row r="130">
@@ -2766,14 +2766,14 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Location de salles</t>
+          <t>Certificat de commercialisation libre</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="D130" t="n">
-        <v>2472.5537109375</v>
+        <v>411.2898445838081</v>
       </c>
     </row>
     <row r="131">
@@ -2784,14 +2784,14 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Location de salles</t>
+          <t>Certificat de commercialisation libre</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>46326</v>
+        <v>46295</v>
       </c>
       <c r="D131" t="n">
-        <v>3072.22705078125</v>
+        <v>414.2891439015028</v>
       </c>
     </row>
     <row r="132">
@@ -2802,14 +2802,14 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Location de salles</t>
+          <t>Certificat de commercialisation libre</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
-        <v>46356</v>
+        <v>46326</v>
       </c>
       <c r="D132" t="n">
-        <v>2458.41162109375</v>
+        <v>455.3930705218759</v>
       </c>
     </row>
     <row r="133">
@@ -2820,14 +2820,14 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Location de salles</t>
+          <t>Certificat de commercialisation libre</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
-        <v>46387</v>
+        <v>46356</v>
       </c>
       <c r="D133" t="n">
-        <v>2341.0830078125</v>
+        <v>441.1221109217106</v>
       </c>
     </row>
     <row r="134">
@@ -2838,14 +2838,14 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Légalisation</t>
+          <t>Location de salles</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="D134" t="n">
-        <v>4560.05224609375</v>
+        <v>3050.934589256226</v>
       </c>
     </row>
     <row r="135">
@@ -2856,14 +2856,14 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Légalisation</t>
+          <t>Location de salles</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="D135" t="n">
-        <v>3693.478759765625</v>
+        <v>2824.682111216182</v>
       </c>
     </row>
     <row r="136">
@@ -2874,14 +2874,14 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Légalisation</t>
+          <t>Location de salles</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="D136" t="n">
-        <v>3589.99169921875</v>
+        <v>2588.130680125992</v>
       </c>
     </row>
     <row r="137">
@@ -2892,14 +2892,14 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Légalisation</t>
+          <t>Location de salles</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="D137" t="n">
-        <v>3651.667236328125</v>
+        <v>2332.214062028947</v>
       </c>
     </row>
     <row r="138">
@@ -2910,14 +2910,14 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Légalisation</t>
+          <t>Location de salles</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="D138" t="n">
-        <v>3651.667236328125</v>
+        <v>2357.910104718665</v>
       </c>
     </row>
     <row r="139">
@@ -2928,14 +2928,14 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Légalisation</t>
+          <t>Location de salles</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="D139" t="n">
-        <v>3398.248291015625</v>
+        <v>2255.49200709954</v>
       </c>
     </row>
     <row r="140">
@@ -2946,14 +2946,14 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Légalisation</t>
+          <t>Location de salles</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="D140" t="n">
-        <v>3474.658935546875</v>
+        <v>2258.219109109026</v>
       </c>
     </row>
     <row r="141">
@@ -2964,14 +2964,14 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Légalisation</t>
+          <t>Location de salles</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="D141" t="n">
-        <v>3485.33203125</v>
+        <v>2316.996202117346</v>
       </c>
     </row>
     <row r="142">
@@ -2982,14 +2982,14 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Légalisation</t>
+          <t>Location de salles</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="D142" t="n">
-        <v>3727.888671875</v>
+        <v>2352.892021541642</v>
       </c>
     </row>
     <row r="143">
@@ -3000,14 +3000,14 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Légalisation</t>
+          <t>Location de salles</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
         <v>46326</v>
       </c>
       <c r="D143" t="n">
-        <v>4424.95947265625</v>
+        <v>2577.164849213222</v>
       </c>
     </row>
     <row r="144">
@@ -3018,14 +3018,14 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Légalisation</t>
+          <t>Location de salles</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
         <v>46356</v>
       </c>
       <c r="D144" t="n">
-        <v>4228.6064453125</v>
+        <v>2509.565442812413</v>
       </c>
     </row>
     <row r="145">
@@ -3036,230 +3036,230 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Légalisation</t>
+          <t>Location de salles</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
         <v>46387</v>
       </c>
       <c r="D145" t="n">
-        <v>4046.186767578125</v>
+        <v>2511.994398501908</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>secteur</t>
+          <t>produit</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Légalisation</t>
         </is>
       </c>
       <c r="C146" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="D146" t="n">
-        <v>33333.8984375</v>
+        <v>4290.695276761558</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>secteur</t>
+          <t>produit</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Légalisation</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="D147" t="n">
-        <v>35919.3984375</v>
+        <v>3975.895008565794</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>secteur</t>
+          <t>produit</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Légalisation</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="D148" t="n">
-        <v>33825.515625</v>
+        <v>3512.555926976196</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>secteur</t>
+          <t>produit</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Légalisation</t>
         </is>
       </c>
       <c r="C149" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="D149" t="n">
-        <v>35998.47265625</v>
+        <v>3493.511585678376</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>secteur</t>
+          <t>produit</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Légalisation</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="D150" t="n">
-        <v>34952.30078125</v>
+        <v>3421.492842806277</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>secteur</t>
+          <t>produit</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Légalisation</t>
         </is>
       </c>
       <c r="C151" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="D151" t="n">
-        <v>37643.66015625</v>
+        <v>3252.278565470884</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>secteur</t>
+          <t>produit</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Légalisation</t>
         </is>
       </c>
       <c r="C152" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="D152" t="n">
-        <v>37213.17578125</v>
+        <v>3234.626477328844</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>secteur</t>
+          <t>produit</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Légalisation</t>
         </is>
       </c>
       <c r="C153" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="D153" t="n">
-        <v>36967.07421875</v>
+        <v>3234.626477328844</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>secteur</t>
+          <t>produit</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Légalisation</t>
         </is>
       </c>
       <c r="C154" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="D154" t="n">
-        <v>42682.33984375</v>
+        <v>3189.686118158538</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>secteur</t>
+          <t>produit</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Légalisation</t>
         </is>
       </c>
       <c r="C155" s="2" t="n">
         <v>46326</v>
       </c>
       <c r="D155" t="n">
-        <v>43338.46484375</v>
+        <v>3493.684886524705</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>secteur</t>
+          <t>produit</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Légalisation</t>
         </is>
       </c>
       <c r="C156" s="2" t="n">
         <v>46356</v>
       </c>
       <c r="D156" t="n">
-        <v>41858.08203125</v>
+        <v>3493.684886524705</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>secteur</t>
+          <t>produit</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Légalisation</t>
         </is>
       </c>
       <c r="C157" s="2" t="n">
         <v>46387</v>
       </c>
       <c r="D157" t="n">
-        <v>46054.80859375</v>
+        <v>3497.065971356577</v>
       </c>
     </row>
     <row r="158">
@@ -3270,14 +3270,14 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Hors secteur</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="C158" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="D158" t="n">
-        <v>5119.18603515625</v>
+        <v>31524.85945646739</v>
       </c>
     </row>
     <row r="159">
@@ -3288,14 +3288,14 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Hors secteur</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="C159" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="D159" t="n">
-        <v>4354.353515625</v>
+        <v>30741.04133014856</v>
       </c>
     </row>
     <row r="160">
@@ -3306,14 +3306,14 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Hors secteur</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="C160" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="D160" t="n">
-        <v>4277.31494140625</v>
+        <v>29622.40275520579</v>
       </c>
     </row>
     <row r="161">
@@ -3324,14 +3324,14 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Hors secteur</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="C161" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="D161" t="n">
-        <v>4317.60888671875</v>
+        <v>28960.69356779783</v>
       </c>
     </row>
     <row r="162">
@@ -3342,14 +3342,14 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Hors secteur</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="C162" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="D162" t="n">
-        <v>4270.03515625</v>
+        <v>28675.33003228586</v>
       </c>
     </row>
     <row r="163">
@@ -3360,14 +3360,14 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Hors secteur</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="C163" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="D163" t="n">
-        <v>3755.22119140625</v>
+        <v>28646.05540628477</v>
       </c>
     </row>
     <row r="164">
@@ -3378,14 +3378,14 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Hors secteur</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="C164" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="D164" t="n">
-        <v>3831.6318359375</v>
+        <v>27405.86407582931</v>
       </c>
     </row>
     <row r="165">
@@ -3396,14 +3396,14 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Hors secteur</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="C165" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="D165" t="n">
-        <v>3881.412353515625</v>
+        <v>27228.47230489597</v>
       </c>
     </row>
     <row r="166">
@@ -3414,14 +3414,14 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Hors secteur</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="C166" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="D166" t="n">
-        <v>4067.892578125</v>
+        <v>27168.60396090754</v>
       </c>
     </row>
     <row r="167">
@@ -3432,14 +3432,14 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Hors secteur</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="C167" s="2" t="n">
         <v>46326</v>
       </c>
       <c r="D167" t="n">
-        <v>4695.37744140625</v>
+        <v>29010.12029799016</v>
       </c>
     </row>
     <row r="168">
@@ -3450,14 +3450,14 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Hors secteur</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="C168" s="2" t="n">
         <v>46356</v>
       </c>
       <c r="D168" t="n">
-        <v>3971.300048828125</v>
+        <v>29030.40741646425</v>
       </c>
     </row>
     <row r="169">
@@ -3468,14 +3468,14 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Hors secteur</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="C169" s="2" t="n">
         <v>46387</v>
       </c>
       <c r="D169" t="n">
-        <v>3874.410400390625</v>
+        <v>29058.49511376771</v>
       </c>
     </row>
     <row r="170">
@@ -3486,14 +3486,14 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Industrie</t>
+          <t>Hors secteur</t>
         </is>
       </c>
       <c r="C170" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="D170" t="n">
-        <v>28874.05859375</v>
+        <v>3841.485795590253</v>
       </c>
     </row>
     <row r="171">
@@ -3504,14 +3504,14 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Industrie</t>
+          <t>Hors secteur</t>
         </is>
       </c>
       <c r="C171" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="D171" t="n">
-        <v>32827.8515625</v>
+        <v>3642.196871360996</v>
       </c>
     </row>
     <row r="172">
@@ -3522,14 +3522,14 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Industrie</t>
+          <t>Hors secteur</t>
         </is>
       </c>
       <c r="C172" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="D172" t="n">
-        <v>35004.2421875</v>
+        <v>3777.669732582601</v>
       </c>
     </row>
     <row r="173">
@@ -3540,14 +3540,14 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Industrie</t>
+          <t>Hors secteur</t>
         </is>
       </c>
       <c r="C173" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="D173" t="n">
-        <v>27680.400390625</v>
+        <v>3670.494196777312</v>
       </c>
     </row>
     <row r="174">
@@ -3558,14 +3558,14 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Industrie</t>
+          <t>Hors secteur</t>
         </is>
       </c>
       <c r="C174" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="D174" t="n">
-        <v>30160.85546875</v>
+        <v>3630.40988971062</v>
       </c>
     </row>
     <row r="175">
@@ -3576,14 +3576,14 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Industrie</t>
+          <t>Hors secteur</t>
         </is>
       </c>
       <c r="C175" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="D175" t="n">
-        <v>29885.126953125</v>
+        <v>3524.602509658475</v>
       </c>
     </row>
     <row r="176">
@@ -3594,14 +3594,14 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Industrie</t>
+          <t>Hors secteur</t>
         </is>
       </c>
       <c r="C176" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="D176" t="n">
-        <v>26940.798828125</v>
+        <v>3551.915304288315</v>
       </c>
     </row>
     <row r="177">
@@ -3612,14 +3612,14 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Industrie</t>
+          <t>Hors secteur</t>
         </is>
       </c>
       <c r="C177" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="D177" t="n">
-        <v>28682.19140625</v>
+        <v>3542.43051468512</v>
       </c>
     </row>
     <row r="178">
@@ -3630,14 +3630,14 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Industrie</t>
+          <t>Hors secteur</t>
         </is>
       </c>
       <c r="C178" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="D178" t="n">
-        <v>31769.880859375</v>
+        <v>3518.381069249576</v>
       </c>
     </row>
     <row r="179">
@@ -3648,14 +3648,14 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Industrie</t>
+          <t>Hors secteur</t>
         </is>
       </c>
       <c r="C179" s="2" t="n">
         <v>46326</v>
       </c>
       <c r="D179" t="n">
-        <v>31891.66015625</v>
+        <v>3853.696882476777</v>
       </c>
     </row>
     <row r="180">
@@ -3666,14 +3666,14 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Industrie</t>
+          <t>Hors secteur</t>
         </is>
       </c>
       <c r="C180" s="2" t="n">
         <v>46356</v>
       </c>
       <c r="D180" t="n">
-        <v>31239.185546875</v>
+        <v>3873.303565340429</v>
       </c>
     </row>
     <row r="181">
@@ -3684,14 +3684,14 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Industrie</t>
+          <t>Hors secteur</t>
         </is>
       </c>
       <c r="C181" s="2" t="n">
         <v>46387</v>
       </c>
       <c r="D181" t="n">
-        <v>31729.23046875</v>
+        <v>3884.92640627643</v>
       </c>
     </row>
     <row r="182">
@@ -3702,14 +3702,14 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Industrie</t>
         </is>
       </c>
       <c r="C182" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="D182" t="n">
-        <v>31185.07421875</v>
+        <v>38372.02346335704</v>
       </c>
     </row>
     <row r="183">
@@ -3720,14 +3720,14 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Industrie</t>
         </is>
       </c>
       <c r="C183" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="D183" t="n">
-        <v>24845.982421875</v>
+        <v>35951.88050198683</v>
       </c>
     </row>
     <row r="184">
@@ -3738,14 +3738,14 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Industrie</t>
         </is>
       </c>
       <c r="C184" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="D184" t="n">
-        <v>24781.83984375</v>
+        <v>31429.30638163631</v>
       </c>
     </row>
     <row r="185">
@@ -3756,14 +3756,14 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Industrie</t>
         </is>
       </c>
       <c r="C185" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="D185" t="n">
-        <v>26757.34375</v>
+        <v>33058.96585723756</v>
       </c>
     </row>
     <row r="186">
@@ -3774,14 +3774,14 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Industrie</t>
         </is>
       </c>
       <c r="C186" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="D186" t="n">
-        <v>28019.421875</v>
+        <v>31396.98077249714</v>
       </c>
     </row>
     <row r="187">
@@ -3792,14 +3792,14 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Industrie</t>
         </is>
       </c>
       <c r="C187" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="D187" t="n">
-        <v>28292.296875</v>
+        <v>31895.83750219073</v>
       </c>
     </row>
     <row r="188">
@@ -3810,14 +3810,14 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Industrie</t>
         </is>
       </c>
       <c r="C188" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="D188" t="n">
-        <v>28458.69140625</v>
+        <v>29593.40310150725</v>
       </c>
     </row>
     <row r="189">
@@ -3828,14 +3828,14 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Industrie</t>
         </is>
       </c>
       <c r="C189" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="D189" t="n">
-        <v>28039.7265625</v>
+        <v>28333.43028613494</v>
       </c>
     </row>
     <row r="190">
@@ -3846,14 +3846,14 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Industrie</t>
         </is>
       </c>
       <c r="C190" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="D190" t="n">
-        <v>28668.8359375</v>
+        <v>28234.11043001682</v>
       </c>
     </row>
     <row r="191">
@@ -3864,14 +3864,14 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Industrie</t>
         </is>
       </c>
       <c r="C191" s="2" t="n">
         <v>46326</v>
       </c>
       <c r="D191" t="n">
-        <v>32173.3125</v>
+        <v>29291.91441410331</v>
       </c>
     </row>
     <row r="192">
@@ -3882,14 +3882,14 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Industrie</t>
         </is>
       </c>
       <c r="C192" s="2" t="n">
         <v>46356</v>
       </c>
       <c r="D192" t="n">
-        <v>28764.181640625</v>
+        <v>28668.32982970076</v>
       </c>
     </row>
     <row r="193">
@@ -3900,14 +3900,230 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Industrie</t>
         </is>
       </c>
       <c r="C193" s="2" t="n">
         <v>46387</v>
       </c>
       <c r="D193" t="n">
-        <v>31204.845703125</v>
+        <v>28755.02289181397</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>secteur</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="n">
+        <v>46053</v>
+      </c>
+      <c r="D194" t="n">
+        <v>31637.23327646248</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>secteur</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D195" t="n">
+        <v>32319.16744341718</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>secteur</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="n">
+        <v>46112</v>
+      </c>
+      <c r="D196" t="n">
+        <v>28128.59229666477</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>secteur</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="D197" t="n">
+        <v>28368.90510070328</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>secteur</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="D198" t="n">
+        <v>28264.85097271445</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>secteur</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="n">
+        <v>46203</v>
+      </c>
+      <c r="D199" t="n">
+        <v>27545.60894883616</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>secteur</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D200" t="n">
+        <v>26750.3120179923</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>secteur</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D201" t="n">
+        <v>26750.3120179923</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>secteur</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="D202" t="n">
+        <v>26568.74948528856</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>secteur</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="n">
+        <v>46326</v>
+      </c>
+      <c r="D203" t="n">
+        <v>27945.42990023349</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>secteur</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="n">
+        <v>46356</v>
+      </c>
+      <c r="D204" t="n">
+        <v>28500.6735687346</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>secteur</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="n">
+        <v>46387</v>
+      </c>
+      <c r="D205" t="n">
+        <v>28528.24875199584</v>
       </c>
     </row>
   </sheetData>
